--- a/tame_output/ON/bt/strategyON_20230812.xlsx
+++ b/tame_output/ON/bt/strategyON_20230812.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1686"/>
+  <dimension ref="A1:G1687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40288,7 +40288,7 @@
         <v>45148</v>
       </c>
       <c r="B1686" t="n">
-        <v>2.885818267569</v>
+        <v>2.885916974141066</v>
       </c>
       <c r="C1686" t="n">
         <v>2.988521600156002</v>
@@ -40304,6 +40304,29 @@
       </c>
       <c r="G1686" t="n">
         <v>4.289923670711938</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="2" t="n">
+        <v>45149</v>
+      </c>
+      <c r="B1687" t="n">
+        <v>2.885101320666294</v>
+      </c>
+      <c r="C1687" t="n">
+        <v>2.990153375390339</v>
+      </c>
+      <c r="D1687" t="n">
+        <v>1.542468294513159</v>
+      </c>
+      <c r="E1687" t="n">
+        <v>3.606784268881855</v>
+      </c>
+      <c r="F1687" t="n">
+        <v>2.170714973119575</v>
+      </c>
+      <c r="G1687" t="n">
+        <v>4.292582359262085</v>
       </c>
     </row>
   </sheetData>
